--- a/Dashboards/data/Data final/ingresos/ingresos_educacion.xlsx
+++ b/Dashboards/data/Data final/ingresos/ingresos_educacion.xlsx
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>176.16</v>
+        <v>180.17</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>445.38</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>190.41</v>
+        <v>192.56</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>479.39</v>
+        <v>489.84</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>188.9</v>
+        <v>190.45</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>475.87</v>
+        <v>482.09</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>191.45</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>476.33</v>
+        <v>470.53</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>204.76</v>
+        <v>215.98</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>496.98</v>
+        <v>529.13</v>
       </c>
     </row>
   </sheetData>
